--- a/AAII_Financials/Quarterly/ZBH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZBH_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2086700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2243800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2001400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2077300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1909100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2023200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1824200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1942000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1889200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1940100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1753600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1869600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1831000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1825100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1669800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1781800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1663200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1777200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1685400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1763300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1601400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2085300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1929300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1226100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1783800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2125700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1892400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1988600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1975500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2071000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1836700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2007600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2017600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2068300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1813100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1949500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1972400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2013100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1832800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>564200</v>
+        <v>635500</v>
       </c>
       <c r="E9" s="3">
+        <v>594200</v>
+      </c>
+      <c r="F9" s="3">
         <v>795500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>559300</v>
       </c>
-      <c r="G9" s="3">
-        <v>590700</v>
-      </c>
       <c r="H9" s="3">
+        <v>592200</v>
+      </c>
+      <c r="I9" s="3">
         <v>549800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>575200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>538600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>553600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>512300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>530600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>518600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>525500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>520300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>488200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>511000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>536500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>491400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>496200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>436300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>647300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>569400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>424500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>471500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>646400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>524400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>573900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>546200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>530700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>533900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>594200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>586900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>608500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>506000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>521800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>501800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>621800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>479300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1522500</v>
+        <v>1541500</v>
       </c>
       <c r="E10" s="3">
+        <v>1492500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1448300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1442100</v>
       </c>
-      <c r="G10" s="3">
-        <v>1486600</v>
-      </c>
       <c r="H10" s="3">
+        <v>1485100</v>
+      </c>
+      <c r="I10" s="3">
         <v>1359300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1448000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1285600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1388400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1376900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1409500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1235000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1344100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1330200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1304800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1181600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1270800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1163200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1240700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1194000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1267100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1165100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1438000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1359900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>801600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1312300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1479300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1368000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1414700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1429300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1540300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1302800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1413400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1430700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1459800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1307100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1427700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1470600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1391300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1353500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E12" s="3">
         <v>103400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>118700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>115900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>113300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>110600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>108500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>111600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>109400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>113300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>116900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>118100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>110400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>108000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>101700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>99400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>96900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>96000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>93800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>165000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>81000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>100000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>85900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>87700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>98400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>121100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>114400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>112100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>101700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>101200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>95700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>99100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>95700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>95000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>91200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>92600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>91100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>95700</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>95600</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>38900</v>
+        <v>65700</v>
       </c>
       <c r="E14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F14" s="3">
         <v>152100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9900</v>
       </c>
-      <c r="G14" s="3">
-        <v>103200</v>
-      </c>
       <c r="H14" s="3">
+        <v>101700</v>
+      </c>
+      <c r="I14" s="3">
         <v>48700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>110400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>40400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>50100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>125800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>108600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>34300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>30100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>46400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>366500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>48200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>62300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>52600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>240000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>47600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>34800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>50800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>35100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>72900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>677800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>61200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>103300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>30400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1030300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>53400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>105200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>405400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>145400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>149200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>110100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>214800</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>170400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E15" s="3">
         <v>162100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>177700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>176500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>160600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>151000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>157600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>148200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>144000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>142100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>144900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>145000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>138200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>133400</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>131500</v>
       </c>
       <c r="R15" s="3">
         <v>131500</v>
       </c>
       <c r="S15" s="3">
+        <v>131500</v>
+      </c>
+      <c r="T15" s="3">
         <v>133000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>130800</v>
       </c>
       <c r="U15" s="3">
         <v>130800</v>
       </c>
       <c r="V15" s="3">
+        <v>130800</v>
+      </c>
+      <c r="W15" s="3">
         <v>132200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>132900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>133600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>152600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>149700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>147700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>147600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>147400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>146600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>146900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>143400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>148000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>147600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>149500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>150800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>151500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>152700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>147700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>152000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>141200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>164300</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1675900</v>
+        <v>1786000</v>
       </c>
       <c r="E17" s="3">
+        <v>1705900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1930400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1661100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1671800</v>
-      </c>
       <c r="H17" s="3">
+        <v>1673300</v>
+      </c>
+      <c r="I17" s="3">
         <v>1568300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1544300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1503600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1540200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1496700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1472100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1451900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1508500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1456200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1853400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1424500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1464800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1808500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1442400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1538500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1342700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1844600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1630100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2239800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1788900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1646600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1783900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1625300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2861500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1613400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1711600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1712600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2108400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1601900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1669400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1624300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1829800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1637300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>410800</v>
+        <v>391000</v>
       </c>
       <c r="E18" s="3">
+        <v>380800</v>
+      </c>
+      <c r="F18" s="3">
         <v>313400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>340300</v>
       </c>
-      <c r="G18" s="3">
-        <v>405500</v>
-      </c>
       <c r="H18" s="3">
+        <v>404000</v>
+      </c>
+      <c r="I18" s="3">
         <v>340800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>478900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>320600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>401800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>392500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>468000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>301700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>361100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>374800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>245300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>280900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>198400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-31300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>243000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>224800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>258700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>240700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>299200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-171700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-456000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>336800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>245800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>204700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>350200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-790500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>223300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>296000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>305000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-40100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>211200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>280100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>348100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>183300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-25400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-42600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-56100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-62400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>571100</v>
+        <v>557100</v>
       </c>
       <c r="E21" s="3">
+        <v>541100</v>
+      </c>
+      <c r="F21" s="3">
         <v>499600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>521200</v>
       </c>
-      <c r="G21" s="3">
-        <v>567700</v>
-      </c>
       <c r="H21" s="3">
+        <v>566200</v>
+      </c>
+      <c r="I21" s="3">
         <v>495000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>619000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>473300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>547400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>533700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>588300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>449700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>496600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>514800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>196300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>451300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>471000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>376100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>198100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>476300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>468600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>502100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>514100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>568400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>87800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-200200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>595300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>492800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>452800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>597300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-542800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>482400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>555100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>565700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>220200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>475900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>542600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>615600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>372900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>483100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E22" s="3">
         <v>68800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>71900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>75400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>79300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>42600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>42300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>38800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>52600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>54700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>53100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>54000</v>
       </c>
       <c r="AA22" s="3">
         <v>54000</v>
       </c>
       <c r="AB22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>50700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>52200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>56700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>59500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>57900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>68300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>68200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>75700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>78800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>79900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>82200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>82100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>82800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>90100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E23" s="3">
         <v>301300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>97900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>279200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>224600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>229100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>289100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>230400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>302200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>215100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>284500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>219300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>276700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>286800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-74800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>177600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>199500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>101200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-83900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>190700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>178100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>214100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>195600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>255800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-221900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-503900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>289200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>184600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>140300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>291700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-865900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>153600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>223400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-124200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>127200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>196400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>265200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>30800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E24" s="3">
         <v>63000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-39900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>46500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>48900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-18900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>42300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-135200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>56400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>66900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>45500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-29200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>33300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-139700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>19000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-247400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>45500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>28300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>32900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>47200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-83000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>28400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>12300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-34100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-38900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-54400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E26" s="3">
         <v>238300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>137800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>231200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>153400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>182600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>240200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>249300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>243100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>172800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>419700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>162900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>209800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-130200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>194200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>154000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>73200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-54700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>162400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>144800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>193000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>335300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>241500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-208900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-492200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>270200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>432000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>131900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>246200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-894200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>162100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>184900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>176200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-41200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>98800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>184100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>299300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>69700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>157900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E27" s="3">
         <v>238100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>139300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>230900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>152800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>182000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>239500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>249100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>242800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>172400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>419200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>162700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>209600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>232500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-130500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>194000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>153700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>73000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-54800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>162200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>144200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>193400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>335200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>237900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-207300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-491600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>269500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>431100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>133700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>246100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-892800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>162200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>185000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>174700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-41000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>98800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>184200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>299400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>69600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>158800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3204,37 +3265,37 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-58800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-30900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-26200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-17700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>4600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>51200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1272400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>25400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>42600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>56100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>4200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>62400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E33" s="3">
         <v>238100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>139300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>230900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>152800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>182000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>239500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>249100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>242800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>172400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>419200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>162700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>209600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>232500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-130500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>194000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>153700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-85700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>136000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>126500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>194700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>333700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>242500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-206600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-508500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>320700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>431100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>133700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>246100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-901100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>162200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>185000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>174700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1231400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>98800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>184200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>299400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>69600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>158800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E35" s="3">
         <v>238100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>139300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>230900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>152800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>182000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>239500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>249100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>242800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>172400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>419200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>162700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>209600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>232500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-130500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>194000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>153700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-85700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>136000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>126500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>194700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>333700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>242500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-206600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-508500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>320700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>431100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>133700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>246100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-901100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>162200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>185000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>174700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1231400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>98800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>184200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>299400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>69600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>158800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,154 +4305,158 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E41" s="3">
         <v>424200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>591900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1292700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>556900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1384500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>525500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>569000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>420100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>393000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>415800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>292100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>319800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>330200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>375700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>545400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>386400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>435800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>478500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>919600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1042400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>724300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>802100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>967300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>713400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2433600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>617900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>512500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>403100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>586800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>542800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>524600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>481200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1765400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>524400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>480800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>450000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1039500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>634100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>475300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E42" s="3">
         <v>54300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4454,550 +4544,565 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AO42" s="3">
-        <v>0</v>
-      </c>
       <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1769500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1728600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1704400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1598300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1611300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1533400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1480700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1481500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1418000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1446400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1442400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1340700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1367300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1380900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1381500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1278500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1282100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1254200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1404900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1392000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1420400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1380200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1452700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1340700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1064500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1039100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1363900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1150800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1247100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1225300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1275800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1262700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1335300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1418500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1544100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1548100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1423000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1600100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1604400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1603600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2270300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2246800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2286400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2483700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2454200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2244200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2235300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2368700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2369900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2388200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2385200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2323300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2275800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2241300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2147200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2128600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2122700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2132100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2394500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2517400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2533000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2511700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2450700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2492200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2496500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2463200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2385000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2362300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2344500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2310200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2256500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2219500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2158500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2125900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4136600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2084200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2023900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1977000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1959400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2070000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E45" s="3">
         <v>52400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>46900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>89300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>80400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>70100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>59600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>79000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>522900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>581900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>671700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>694700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>607100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>483400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>361000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>383900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>377800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>352400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>432400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>435000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>357100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>375900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>396500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>376900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>352300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>506500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>500200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>465500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>856000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>320200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>527200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>463300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>465700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>535800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5096700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4962500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5119900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5834900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5053900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5590200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4671500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4864000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4639400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4631500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4609500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4372000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4387900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4411900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4427300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4534400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4462900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4516800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4885000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5312400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5356800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5000100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5083300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5152600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4706800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6370900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4723900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4401500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4391200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4499200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4427400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4513300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4475200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5775300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4564800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4433300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4424100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5079900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4663600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4698100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>400</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4400</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2236800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2211700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2411300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2194300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2175700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2064900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2262300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2107200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2103000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2090900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2264200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2032200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1975000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1906400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1872500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1801600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1796600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1825900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2016500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2008200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2005200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2021900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2047700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2042500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2056500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2065500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2344100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2314600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2293400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2276600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2015400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2002400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1986900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2031300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4077200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2048600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2057400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2053200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2037900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2080800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14381100</v>
+      </c>
+      <c r="E49" s="3">
         <v>14479400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14664400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14441700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14600300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13456600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13549500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13577600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13531900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13525600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13674900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13602100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13771400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13806600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13644000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13935300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14173300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14287400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15492000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>15682300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>15890300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16034400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16317300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15889400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15919800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>16028900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>16857300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>16884800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>17117900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>17092500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>17279000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>18421000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>18592500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>18964800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>29690200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>19369800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>19409500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>19335700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>19429300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>19771200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1082800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1068000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>875400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1001900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1015600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1037900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>833300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1153300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1177100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>942900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1197300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1155600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1118600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1122200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1062000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1019900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>987400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1062900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1005700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>970900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>970200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>969400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>941000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>964500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1047600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>713400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>714300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>403200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>420700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>405000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>445300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>436200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>409800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>777600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>565800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>568200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>519000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>553600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>486400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22797800</v>
+      </c>
+      <c r="E54" s="3">
         <v>22721600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23091700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23488000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22865100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22183900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21365300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21720300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21520000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21452400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21496900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21217300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21294300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21243500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21066000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21333300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21452700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21617500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23456400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24008600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24223200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24026600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24417700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24025500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23647600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25512900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24638700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>24315200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24205700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24289000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24126800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25382000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25490800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27181200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>26014000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>26417500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>26459200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>26987800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>26684400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>27036500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>352400</v>
+      </c>
+      <c r="E57" s="3">
         <v>361200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>303000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>315300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>348700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>301300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>194600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>322400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>341800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>370300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>410600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>319700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>354600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>397100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>354100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>333900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>307100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>322000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>351200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>327600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>360600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>329800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>330000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>334800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>363400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>404900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>400900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>355200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>347500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>361100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>362600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>345800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>355700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>347300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>330200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>327100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>360200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>335900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>364500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1201500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1175900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>654000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>609400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>847900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>612800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>928200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1773300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1908700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1005000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>986200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>360000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>520000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>585000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>544300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>659100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>851900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1014500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1605100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1045700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1050000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>300000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>500000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>450000</v>
       </c>
       <c r="AA58" s="3">
         <v>450000</v>
       </c>
       <c r="AB58" s="3">
+        <v>450000</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1950000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1500000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>2000000</v>
       </c>
       <c r="AE58" s="3">
         <v>2000000</v>
       </c>
       <c r="AF58" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AG58" s="3">
         <v>500000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>525000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>600000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1625000</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>1225000</v>
       </c>
       <c r="AL58" s="3">
         <v>1225000</v>
       </c>
       <c r="AM58" s="3">
+        <v>1225000</v>
+      </c>
+      <c r="AN58" s="3">
         <v>1329300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>975000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>575600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>575800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1125300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1033300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>72100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1478200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1502900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1380800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1475600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1357900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1421700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1391800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1359100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1119600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1459800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1302700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1304600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1337600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1511600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1565800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1517900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1459600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1726900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1481400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1347800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1424700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1540600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1418700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1330300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1393900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1533700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1445400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1397900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1452200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4117800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1458100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1306900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1345200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1441400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1470000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3013500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2864300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2583700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2402900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2699500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2294900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2450900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3571300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3608400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2797000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2857400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2071500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2233700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2335900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2358200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2295700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2463600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2674100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3467900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2939100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2928500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2089400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2556900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2266200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2161200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3779600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3441500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3773900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3677800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2255000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2421300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2391200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1853600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3424500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3069700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3010200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2996400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2656100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2381500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2312100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6400200</v>
+      </c>
+      <c r="E61" s="3">
         <v>6411100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7219900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7627600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6873600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6712600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5692600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4865400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4125900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4998800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5221800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5338400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5397500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5395400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5152200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5055200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5172000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5286300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5463700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6458100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6802500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7538700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7626500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7840200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7759300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7718700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6715000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6345900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6708900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8298100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8413700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8597400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9413300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9486900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8917500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9199700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>9354400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>10537800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10665800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11006200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>515900</v>
+      </c>
+      <c r="E62" s="3">
         <v>514800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>338200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>691500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>757700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>772600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>393100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1036200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>680100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>571900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>824000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>809600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>870000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1528600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1731300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1692500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1635700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1858400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1897200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1908900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1948700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2034900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2040900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2083200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2131900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2089400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2109900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2156800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2196600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2015700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2170400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2179700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2270300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2858500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3757400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3828900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3859700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3967200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3972000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10165200</v>
+      </c>
+      <c r="E66" s="3">
         <v>10040100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10385900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10722000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10330800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9780100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8889100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9337100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8770500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8846300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9008700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8699300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8915700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9085900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9045700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9088600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9334300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9602000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10795700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11300000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11645300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11581600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12223500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12153300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12006200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13634300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12250600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12233700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12546600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12754600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12855500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13165200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13447700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15182800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14278200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15967700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>16180300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17054400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17015500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>17291000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11955100</v>
+      </c>
+      <c r="E72" s="3">
         <v>11802500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11611000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11518600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11335200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11229700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11095300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10903700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10702500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10509000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10384500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10014900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9902300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9741700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9559300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9739900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9606500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9503100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10292200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10426300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10331000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10237700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10086900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9802900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9610000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9866200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10427300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10155300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9772700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9688100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9491200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10441200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10327900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10191700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10022800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8837200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8787600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8649600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8467100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>8442700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12623900</v>
+      </c>
+      <c r="E76" s="3">
         <v>12673300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12697700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12756500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12525000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12395100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12468100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12374700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12741100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12598000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12480500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12510800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12371500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12150700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12020300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12244700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12118400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12015500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12660700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12708600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12577900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12445000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12194200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11872200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11641400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11878600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12388100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12081500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11659100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11534400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11271300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12216800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12043100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11998400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11735800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10449800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10278900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9933400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>9668900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9745500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E81" s="3">
         <v>238100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>139300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>230900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>152800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>182000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>239500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>249100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>242800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>172400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>419200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>162700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>209600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>232500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-130500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>194000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>153700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-85700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>136000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>126500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>194700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>333700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>242500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-206600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-508500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>320700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>431100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>133700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>246100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-901100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>162200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>185000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>174700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1231400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>98800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>184200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>299400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>69600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>158800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E83" s="3">
         <v>103400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>106000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>102700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>99200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>96500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>96300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>96200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>99300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>98400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>97000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>99900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>99700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>103000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>228500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>231400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>232700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>233800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>267100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>265100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>266500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>268700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>265400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>258600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>255700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>253000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>253900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>251500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>253000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>247700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>254800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>260600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>261600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>263500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>264500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>266500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>264100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>267600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>252000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>288100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>447800</v>
+      </c>
+      <c r="E89" s="3">
         <v>359400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>517400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>418700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>378200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>382800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>506300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>395700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>369400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>228000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>588400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>337600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>347900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>307700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>244200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>450800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>352500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>237200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>365700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>433100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>453900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>246500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>425100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>381300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>450900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>423300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>577900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>301000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>283600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>379500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>484100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>393300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>490500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>402900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>463500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>440500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>275400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>627200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>352600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-139600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-113500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-149100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-141000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-130600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-103400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-117900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-137100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-141700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-148800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-182800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-129500</v>
       </c>
       <c r="Q91" s="3">
         <v>-129500</v>
       </c>
       <c r="R91" s="3">
+        <v>-129500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-118800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-105100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-92800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-119800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-113700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-40200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-37800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-27000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-26700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-46200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-129500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-148800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-150400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-190800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-159000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-322000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-163300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1384400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-106000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-291200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-154900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-247000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-195000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-220800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-165600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-243100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-149400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-112500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-243200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-88300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-146200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-125200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-109900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-122300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-315900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-91400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-85300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-121200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-138000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-163600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-322200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-105500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-82400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-138900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-93600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-101700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-128200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-120500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-133100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-146800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1374300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,16 +10455,17 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E96" s="3">
         <v>46900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>47500</v>
       </c>
       <c r="F96" s="3">
         <v>47500</v>
@@ -10240,112 +10474,115 @@
         <v>47500</v>
       </c>
       <c r="H96" s="3">
+        <v>47500</v>
+      </c>
+      <c r="I96" s="3">
         <v>47800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>48000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>49200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>49400</v>
       </c>
       <c r="L96" s="3">
         <v>49400</v>
       </c>
       <c r="M96" s="3">
+        <v>49400</v>
+      </c>
+      <c r="N96" s="3">
         <v>50200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>50100</v>
-      </c>
-      <c r="O96" s="3">
-        <v>50300</v>
       </c>
       <c r="P96" s="3">
         <v>50300</v>
       </c>
       <c r="Q96" s="3">
+        <v>50300</v>
+      </c>
+      <c r="R96" s="3">
         <v>-50400</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-50300</v>
       </c>
       <c r="S96" s="3">
         <v>-50300</v>
       </c>
       <c r="T96" s="3">
-        <v>-50200</v>
+        <v>-50300</v>
       </c>
       <c r="U96" s="3">
         <v>-50200</v>
       </c>
       <c r="V96" s="3">
+        <v>-50200</v>
+      </c>
+      <c r="W96" s="3">
         <v>-50100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-50000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-49800</v>
       </c>
       <c r="Y96" s="3">
         <v>-49800</v>
       </c>
       <c r="Z96" s="3">
-        <v>-49600</v>
+        <v>-49800</v>
       </c>
       <c r="AA96" s="3">
         <v>-49600</v>
       </c>
       <c r="AB96" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-49500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-49400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-49200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-49100</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-49000</v>
       </c>
       <c r="AG96" s="3">
         <v>-49000</v>
       </c>
       <c r="AH96" s="3">
-        <v>-48800</v>
+        <v>-49000</v>
       </c>
       <c r="AI96" s="3">
         <v>-48800</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-48600</v>
+        <v>-48800</v>
       </c>
       <c r="AK96" s="3">
         <v>-48600</v>
       </c>
       <c r="AL96" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-48500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-48400</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-48100</v>
       </c>
       <c r="AO96" s="3">
         <v>-48100</v>
       </c>
       <c r="AP96" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-47900</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-271100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-369200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-897000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>483800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>163800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>575400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-240600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-101900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-91900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-50100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-251400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-196000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-109400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-206700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-313400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-193900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-146000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-190500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-655800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-426100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-28300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-195800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-286300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1585700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1492800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-182700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-298400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-163600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-275500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-297700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1570800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>841800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-232900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-320700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-913000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>256100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-309100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>519200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E101" s="3">
         <v>7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-12700</v>
       </c>
       <c r="O101" s="3">
         <v>-12700</v>
       </c>
       <c r="P101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-12700</v>
       </c>
       <c r="S101" s="3">
         <v>-12700</v>
       </c>
       <c r="T101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>1100</v>
       </c>
       <c r="AF101" s="3">
         <v>1100</v>
       </c>
       <c r="AG101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>10400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>12000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>7000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-12500</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-167700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>735800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-827800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>859200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>148900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>123600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-169700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>159000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-49400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-42700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-441100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-122800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>318100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-77800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-165200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>253900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1720200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1815700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>105400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>109400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-183700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>44000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>43400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1284200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1241000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>43600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>30800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-589500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>405400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>158800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-501000</v>
       </c>
     </row>
